--- a/AAII_Financials/Yearly/PLUS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PLUS_YR_FIN.xlsx
@@ -2972,7 +2972,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>125100</v>
+        <v>125300</v>
       </c>
       <c r="E58" s="3">
         <v>95100</v>
@@ -3023,7 +3023,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>199900</v>
+        <v>199700</v>
       </c>
       <c r="E59" s="3">
         <v>337400</v>
@@ -3125,7 +3125,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>10800</v>
+        <v>10700</v>
       </c>
       <c r="E61" s="3">
         <v>13500</v>
@@ -3176,7 +3176,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E62" s="3">
         <v>12600</v>
